--- a/data/output/stats-scottsdale-fall_2026.xlsx
+++ b/data/output/stats-scottsdale-fall_2026.xlsx
@@ -820,12 +820,12 @@
           <t>Team OPS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Through Date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Workbook Season</t>
         </is>
@@ -850,7 +850,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>0.956</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1325,13 +1325,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -2140,13 +2140,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -2518,13 +2518,13 @@
         <v>55</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>4</v>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>0.956</t>
         </is>
       </c>
     </row>
@@ -3018,13 +3018,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -3396,13 +3396,13 @@
         <v>55</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>4</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>0.956</t>
         </is>
       </c>
     </row>
@@ -4774,13 +4774,13 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
@@ -5152,14 +5152,14 @@
         <v>21</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0</v>
@@ -5186,22 +5186,22 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>0.953</t>
         </is>
       </c>
     </row>

--- a/data/output/stats-scottsdale-fall_2026.xlsx
+++ b/data/output/stats-scottsdale-fall_2026.xlsx
@@ -14,14 +14,18 @@
     <sheet name="DCK Fall 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="DCK Fall 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="DCK Fall 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DCK Fall 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DCK Fall 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DCK Total'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DCK Fall 2026 Total'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DCK Total'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DCK Fall 2026 Total'!$A$1:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DCK Fall 2026 Game 1'!$A$1:$Q$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DCK Fall 2026 Game 2'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DCK Fall 2026 Game 3'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DCK Fall 2026 Game 4'!$A$1:$Q$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -843,34 +847,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.432</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.608</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>1.030</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -888,821 +892,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>HRO</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>RBI</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>OBP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>SLG</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Blake</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cory</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1.200</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Jakob</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.200</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.200</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.200</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Jason</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.800</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1.400</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Logan</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Marques</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0.833</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.200</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.950</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.200</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.200</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.200</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Q12"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF0000FF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1822,19 +1011,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1852,29 +1041,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.250</t>
         </is>
       </c>
     </row>
@@ -1885,59 +1074,59 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>1.333</t>
         </is>
       </c>
     </row>
@@ -1948,59 +1137,59 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.227</t>
         </is>
       </c>
     </row>
@@ -2011,16 +1200,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2044,26 +1233,26 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.364</t>
         </is>
       </c>
     </row>
@@ -2133,70 +1322,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.625</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marques</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2206,13 +1395,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2230,58 +1419,58 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Marques</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2293,55 +1482,55 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>1.143</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.643</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -2359,49 +1548,49 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.385</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.950</t>
+          <t>0.885</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2426,165 +1615,228 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.231</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Skip</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B14" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C14" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>0.200</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>0.200</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>0.200</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>0.400</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.407</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0.956</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF00FF00"/>
+    <tabColor rgb="FF0000FF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2700,19 +1952,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2730,29 +1982,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.250</t>
         </is>
       </c>
     </row>
@@ -2763,59 +2015,59 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>1.333</t>
         </is>
       </c>
     </row>
@@ -2826,59 +2078,59 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.227</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2141,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2922,26 +2174,26 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.364</t>
         </is>
       </c>
     </row>
@@ -3011,70 +2263,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.625</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marques</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3084,13 +2336,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3108,58 +2360,58 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Marques</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3171,55 +2423,55 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>1.143</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.643</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -3237,49 +2489,49 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.200</t>
+          <t>0.385</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.950</t>
+          <t>0.885</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3304,153 +2556,1283 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.429</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.231</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Skip</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.400</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0.432</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.422</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0.608</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1.030</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF00FF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.583</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.583</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.583</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.583</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.545</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.727</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.227</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jakob</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.364</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.800</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1.400</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.625</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.625</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marques</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.143</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.643</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.385</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.885</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.429</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.429</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.231</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.100</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C14" t="n">
         <v>5</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>0.200</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>0.200</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>0.200</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>0.400</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="C14" s="2" t="n">
+      <c r="B16" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.407</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.400</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0.956</t>
+      <c r="E16" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0.432</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.422</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0.608</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1.030</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5209,4 +5591,1634 @@
   <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jakob</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Marques</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.789</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.289</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jakob</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.334</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Marques</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.394</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.394</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.485</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.879</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/output/stats-scottsdale-fall_2026.xlsx
+++ b/data/output/stats-scottsdale-fall_2026.xlsx
@@ -12,20 +12,20 @@
     <sheet name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="DCK Total" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="DCK Fall 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DCK Fall 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DCK Fall 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCK Fall 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="DCK Fall 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="DCK Fall 2026 Game 4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DCK Fall 2026 Game 3" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DCK Fall 2026 Game 2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DCK Fall 2026 Game 1" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DCK Total'!$A$1:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DCK Fall 2026 Total'!$A$1:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DCK Fall 2026 Game 1'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DCK Fall 2026 Game 2'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DCK Fall 2026 Game 3'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DCK Fall 2026 Game 4'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DCK Fall 2026 Game 4'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DCK Fall 2026 Game 3'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'DCK Fall 2026 Game 2'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'DCK Fall 2026 Game 1'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3844,7 +3844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3990,10 +3990,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -4208,23 +4208,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4242,29 +4242,29 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -4305,29 +4305,29 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -4350,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
@@ -4404,16 +4404,16 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4425,61 +4425,61 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -4497,33 +4497,33 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4557,10 +4557,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -4583,139 +4583,891 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Skip</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.666</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C13" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D13" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0.394</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0.394</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.576</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0.970</t>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.485</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.879</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HRO</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RBI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OBP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Blake</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cory</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jakob</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Marques</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pat</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.789</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.289</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -5593,14 +6345,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5716,19 +6468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -5753,22 +6505,22 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -5779,16 +6531,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -5809,29 +6561,29 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.750</t>
         </is>
       </c>
     </row>
@@ -5842,16 +6594,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -5866,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -5879,22 +6631,22 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -5911,10 +6663,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -5938,49 +6690,49 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6001,46 +6753,46 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>1.750</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2.750</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marques</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -6049,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -6061,10 +6813,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -6078,19 +6830,19 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Marques</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6100,13 +6852,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6127,33 +6879,33 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>0.750</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6163,13 +6915,13 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -6190,26 +6942,26 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.250</t>
         </is>
       </c>
     </row>
@@ -6220,22 +6972,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -6244,35 +6996,35 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.833</t>
         </is>
       </c>
     </row>
@@ -6289,10 +7041,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6313,912 +7065,160 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+          <t>0.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Skip</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0.789</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1.289</t>
+      <c r="B14" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.394</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.394</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.970</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>SF</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>HRO</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>RBI</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>OBP</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>SLG</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Blake</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cory</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.666</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Jakob</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Josh</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Logan</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.334</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Marques</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mike</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Pat</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.333</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.250</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0.394</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.394</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0.485</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0.879</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>